--- a/đầu vào/tháng 7/TK 336 - PCVT.xlsx
+++ b/đầu vào/tháng 7/TK 336 - PCVT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\DATA KTTH\KIEMDO_136-336\đầu vào\tháng 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217CAF6B-DD1A-488C-9659-FBA13C714CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC5369D-A60C-40A2-8E3D-41E28BF42306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{08216DBB-2041-48FD-BCB8-9ADD1D61929B}"/>
   </bookViews>
@@ -3789,7 +3789,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4011,6 +4011,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="18">
     <border>
@@ -4271,7 +4289,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4361,6 +4379,12 @@
     <xf numFmtId="164" fontId="20" fillId="37" borderId="11" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="20" fillId="38" borderId="11" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="39" borderId="11" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -4369,6 +4393,25 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="34" borderId="10" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="34" borderId="17" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -4391,29 +4434,13 @@
     <xf numFmtId="0" fontId="21" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="34" borderId="10" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="34" borderId="17" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="40" borderId="11" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="20" fillId="38" borderId="11" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="41" borderId="11" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="39" borderId="11" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="42" borderId="11" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4803,33 +4830,33 @@
       <c r="B3" s="1"/>
     </row>
     <row r="4" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="34"/>
+      <c r="B4" s="43"/>
     </row>
     <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="44"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="35"/>
+      <c r="B6" s="44"/>
     </row>
     <row r="8" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="39"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="36" t="s">
+      <c r="C8" s="48"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="45" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="41" t="s">
@@ -4843,7 +4870,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="37"/>
+      <c r="A9" s="46"/>
       <c r="B9" s="6" t="s">
         <v>10</v>
       </c>
@@ -4853,7 +4880,7 @@
       <c r="D9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="37"/>
+      <c r="E9" s="46"/>
       <c r="F9" s="42"/>
       <c r="G9" s="42"/>
       <c r="H9" s="5" t="s">
@@ -4861,25 +4888,25 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="44"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="45"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="40"/>
     </row>
     <row r="11" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="33"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="35"/>
       <c r="F11" s="22"/>
       <c r="G11" s="23">
         <v>412717361000</v>
@@ -6591,13 +6618,13 @@
       </c>
     </row>
     <row r="83" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="31" t="s">
+      <c r="A83" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="B83" s="32"/>
-      <c r="C83" s="32"/>
-      <c r="D83" s="32"/>
-      <c r="E83" s="33"/>
+      <c r="B83" s="34"/>
+      <c r="C83" s="34"/>
+      <c r="D83" s="34"/>
+      <c r="E83" s="35"/>
       <c r="F83" s="23">
         <v>1442393597159</v>
       </c>
@@ -6607,13 +6634,13 @@
       <c r="H83" s="8"/>
     </row>
     <row r="84" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="31" t="s">
+      <c r="A84" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="B84" s="32"/>
-      <c r="C84" s="32"/>
-      <c r="D84" s="32"/>
-      <c r="E84" s="33"/>
+      <c r="B84" s="34"/>
+      <c r="C84" s="34"/>
+      <c r="D84" s="34"/>
+      <c r="E84" s="35"/>
       <c r="F84" s="22"/>
       <c r="G84" s="23">
         <v>446418087938</v>
@@ -6621,25 +6648,25 @@
       <c r="H84" s="8"/>
     </row>
     <row r="85" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="43" t="s">
+      <c r="A85" s="38" t="s">
         <v>163</v>
       </c>
-      <c r="B85" s="44"/>
-      <c r="C85" s="44"/>
-      <c r="D85" s="44"/>
-      <c r="E85" s="44"/>
-      <c r="F85" s="44"/>
-      <c r="G85" s="44"/>
-      <c r="H85" s="45"/>
+      <c r="B85" s="39"/>
+      <c r="C85" s="39"/>
+      <c r="D85" s="39"/>
+      <c r="E85" s="39"/>
+      <c r="F85" s="39"/>
+      <c r="G85" s="39"/>
+      <c r="H85" s="40"/>
     </row>
     <row r="86" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="31" t="s">
+      <c r="A86" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B86" s="32"/>
-      <c r="C86" s="32"/>
-      <c r="D86" s="32"/>
-      <c r="E86" s="33"/>
+      <c r="B86" s="34"/>
+      <c r="C86" s="34"/>
+      <c r="D86" s="34"/>
+      <c r="E86" s="35"/>
       <c r="F86" s="23">
         <v>3844085208</v>
       </c>
@@ -7271,13 +7298,13 @@
       </c>
     </row>
     <row r="113" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="31" t="s">
+      <c r="A113" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="B113" s="32"/>
-      <c r="C113" s="32"/>
-      <c r="D113" s="32"/>
-      <c r="E113" s="33"/>
+      <c r="B113" s="34"/>
+      <c r="C113" s="34"/>
+      <c r="D113" s="34"/>
+      <c r="E113" s="35"/>
       <c r="F113" s="23">
         <v>723124328</v>
       </c>
@@ -7287,13 +7314,13 @@
       <c r="H113" s="8"/>
     </row>
     <row r="114" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="31" t="s">
+      <c r="A114" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="B114" s="32"/>
-      <c r="C114" s="32"/>
-      <c r="D114" s="32"/>
-      <c r="E114" s="33"/>
+      <c r="B114" s="34"/>
+      <c r="C114" s="34"/>
+      <c r="D114" s="34"/>
+      <c r="E114" s="35"/>
       <c r="F114" s="23">
         <v>3795352626</v>
       </c>
@@ -7301,25 +7328,25 @@
       <c r="H114" s="8"/>
     </row>
     <row r="115" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="43" t="s">
+      <c r="A115" s="38" t="s">
         <v>214</v>
       </c>
-      <c r="B115" s="44"/>
-      <c r="C115" s="44"/>
-      <c r="D115" s="44"/>
-      <c r="E115" s="44"/>
-      <c r="F115" s="44"/>
-      <c r="G115" s="44"/>
-      <c r="H115" s="45"/>
+      <c r="B115" s="39"/>
+      <c r="C115" s="39"/>
+      <c r="D115" s="39"/>
+      <c r="E115" s="39"/>
+      <c r="F115" s="39"/>
+      <c r="G115" s="39"/>
+      <c r="H115" s="40"/>
     </row>
     <row r="116" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="31" t="s">
+      <c r="A116" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B116" s="32"/>
-      <c r="C116" s="32"/>
-      <c r="D116" s="32"/>
-      <c r="E116" s="33"/>
+      <c r="B116" s="34"/>
+      <c r="C116" s="34"/>
+      <c r="D116" s="34"/>
+      <c r="E116" s="35"/>
       <c r="F116" s="22"/>
       <c r="G116" s="23">
         <v>9983257640</v>
@@ -7495,13 +7522,13 @@
       </c>
     </row>
     <row r="124" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="31" t="s">
+      <c r="A124" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="B124" s="32"/>
-      <c r="C124" s="32"/>
-      <c r="D124" s="32"/>
-      <c r="E124" s="33"/>
+      <c r="B124" s="34"/>
+      <c r="C124" s="34"/>
+      <c r="D124" s="34"/>
+      <c r="E124" s="35"/>
       <c r="F124" s="23">
         <v>1345463714</v>
       </c>
@@ -7511,13 +7538,13 @@
       <c r="H124" s="8"/>
     </row>
     <row r="125" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A125" s="31" t="s">
+      <c r="A125" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="B125" s="32"/>
-      <c r="C125" s="32"/>
-      <c r="D125" s="32"/>
-      <c r="E125" s="33"/>
+      <c r="B125" s="34"/>
+      <c r="C125" s="34"/>
+      <c r="D125" s="34"/>
+      <c r="E125" s="35"/>
       <c r="F125" s="22"/>
       <c r="G125" s="23">
         <v>8891367286</v>
@@ -7525,16 +7552,16 @@
       <c r="H125" s="8"/>
     </row>
     <row r="126" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="43" t="s">
+      <c r="A126" s="38" t="s">
         <v>224</v>
       </c>
-      <c r="B126" s="44"/>
-      <c r="C126" s="44"/>
-      <c r="D126" s="44"/>
-      <c r="E126" s="44"/>
-      <c r="F126" s="44"/>
-      <c r="G126" s="44"/>
-      <c r="H126" s="45"/>
+      <c r="B126" s="39"/>
+      <c r="C126" s="39"/>
+      <c r="D126" s="39"/>
+      <c r="E126" s="39"/>
+      <c r="F126" s="39"/>
+      <c r="G126" s="39"/>
+      <c r="H126" s="40"/>
     </row>
     <row r="127" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="14" t="s">
@@ -9589,7 +9616,7 @@
         <v>306</v>
       </c>
       <c r="F218" s="25"/>
-      <c r="G218" s="48">
+      <c r="G218" s="31">
         <v>1963917778</v>
       </c>
       <c r="H218" s="13" t="s">
@@ -9613,7 +9640,7 @@
         <v>365</v>
       </c>
       <c r="F219" s="25"/>
-      <c r="G219" s="48">
+      <c r="G219" s="31">
         <v>3451399200</v>
       </c>
       <c r="H219" s="13" t="s">
@@ -9637,7 +9664,7 @@
         <v>394</v>
       </c>
       <c r="F220" s="25"/>
-      <c r="G220" s="48">
+      <c r="G220" s="31">
         <v>3589537560</v>
       </c>
       <c r="H220" s="13" t="s">
@@ -9661,7 +9688,7 @@
         <v>405</v>
       </c>
       <c r="F221" s="25"/>
-      <c r="G221" s="48">
+      <c r="G221" s="31">
         <v>3951311154</v>
       </c>
       <c r="H221" s="13" t="s">
@@ -9709,7 +9736,7 @@
         <v>402</v>
       </c>
       <c r="F223" s="25"/>
-      <c r="G223" s="49">
+      <c r="G223" s="32">
         <v>6277098679</v>
       </c>
       <c r="H223" s="13" t="s">
@@ -9733,7 +9760,7 @@
         <v>403</v>
       </c>
       <c r="F224" s="25"/>
-      <c r="G224" s="49">
+      <c r="G224" s="32">
         <v>47879803</v>
       </c>
       <c r="H224" s="13" t="s">
@@ -9764,7 +9791,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="10" t="s">
         <v>139</v>
       </c>
@@ -9780,7 +9807,7 @@
       <c r="E226" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="F226" s="24">
+      <c r="F226" s="52">
         <v>86064000</v>
       </c>
       <c r="G226" s="25"/>
@@ -9804,7 +9831,7 @@
       <c r="E227" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="F227" s="24">
+      <c r="F227" s="50">
         <v>198647000</v>
       </c>
       <c r="G227" s="25"/>
@@ -9812,7 +9839,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="10" t="s">
         <v>289</v>
       </c>
@@ -9828,7 +9855,7 @@
       <c r="E228" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="F228" s="24">
+      <c r="F228" s="50">
         <v>6773</v>
       </c>
       <c r="G228" s="25"/>
@@ -9852,7 +9879,7 @@
       <c r="E229" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="F229" s="24">
+      <c r="F229" s="50">
         <v>22</v>
       </c>
       <c r="G229" s="25"/>
@@ -9876,7 +9903,7 @@
       <c r="E230" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="F230" s="24">
+      <c r="F230" s="50">
         <v>237878</v>
       </c>
       <c r="G230" s="25"/>
@@ -9900,7 +9927,7 @@
       <c r="E231" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="F231" s="24">
+      <c r="F231" s="50">
         <v>650855</v>
       </c>
       <c r="G231" s="25"/>
@@ -9924,7 +9951,7 @@
       <c r="E232" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="F232" s="24">
+      <c r="F232" s="50">
         <v>744887</v>
       </c>
       <c r="G232" s="25"/>
@@ -9948,7 +9975,7 @@
       <c r="E233" s="13" t="s">
         <v>367</v>
       </c>
-      <c r="F233" s="24">
+      <c r="F233" s="50">
         <v>13</v>
       </c>
       <c r="G233" s="25"/>
@@ -9972,7 +9999,7 @@
       <c r="E234" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="F234" s="24">
+      <c r="F234" s="50">
         <v>276600000</v>
       </c>
       <c r="G234" s="25"/>
@@ -9996,7 +10023,7 @@
       <c r="E235" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="F235" s="24">
+      <c r="F235" s="50">
         <v>799200000</v>
       </c>
       <c r="G235" s="25"/>
@@ -10020,7 +10047,7 @@
       <c r="E236" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F236" s="24">
+      <c r="F236" s="50">
         <v>282012</v>
       </c>
       <c r="G236" s="25"/>
@@ -10044,7 +10071,7 @@
       <c r="E237" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F237" s="24">
+      <c r="F237" s="50">
         <v>312162</v>
       </c>
       <c r="G237" s="25"/>
@@ -10068,7 +10095,7 @@
       <c r="E238" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F238" s="24">
+      <c r="F238" s="50">
         <v>456000</v>
       </c>
       <c r="G238" s="25"/>
@@ -10092,7 +10119,7 @@
       <c r="E239" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F239" s="24">
+      <c r="F239" s="50">
         <v>476759</v>
       </c>
       <c r="G239" s="25"/>
@@ -10116,7 +10143,7 @@
       <c r="E240" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F240" s="24">
+      <c r="F240" s="50">
         <v>541924</v>
       </c>
       <c r="G240" s="25"/>
@@ -10140,7 +10167,7 @@
       <c r="E241" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F241" s="24">
+      <c r="F241" s="50">
         <v>1063130</v>
       </c>
       <c r="G241" s="25"/>
@@ -10164,7 +10191,7 @@
       <c r="E242" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F242" s="24">
+      <c r="F242" s="50">
         <v>1107131</v>
       </c>
       <c r="G242" s="25"/>
@@ -10188,7 +10215,7 @@
       <c r="E243" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F243" s="24">
+      <c r="F243" s="50">
         <v>1456000</v>
       </c>
       <c r="G243" s="25"/>
@@ -10212,7 +10239,7 @@
       <c r="E244" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F244" s="24">
+      <c r="F244" s="50">
         <v>2171718</v>
       </c>
       <c r="G244" s="25"/>
@@ -10236,7 +10263,7 @@
       <c r="E245" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F245" s="24">
+      <c r="F245" s="50">
         <v>2239885</v>
       </c>
       <c r="G245" s="25"/>
@@ -10260,7 +10287,7 @@
       <c r="E246" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F246" s="24">
+      <c r="F246" s="50">
         <v>2373897</v>
       </c>
       <c r="G246" s="25"/>
@@ -10284,7 +10311,7 @@
       <c r="E247" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F247" s="24">
+      <c r="F247" s="50">
         <v>2405387</v>
       </c>
       <c r="G247" s="25"/>
@@ -10308,7 +10335,7 @@
       <c r="E248" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F248" s="24">
+      <c r="F248" s="50">
         <v>3498676</v>
       </c>
       <c r="G248" s="25"/>
@@ -10332,7 +10359,7 @@
       <c r="E249" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F249" s="24">
+      <c r="F249" s="50">
         <v>3678470</v>
       </c>
       <c r="G249" s="25"/>
@@ -10356,7 +10383,7 @@
       <c r="E250" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F250" s="24">
+      <c r="F250" s="50">
         <v>4332900</v>
       </c>
       <c r="G250" s="25"/>
@@ -10380,7 +10407,7 @@
       <c r="E251" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F251" s="24">
+      <c r="F251" s="50">
         <v>7642834</v>
       </c>
       <c r="G251" s="25"/>
@@ -10404,7 +10431,7 @@
       <c r="E252" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F252" s="24">
+      <c r="F252" s="50">
         <v>9733864</v>
       </c>
       <c r="G252" s="25"/>
@@ -10428,7 +10455,7 @@
       <c r="E253" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F253" s="24">
+      <c r="F253" s="50">
         <v>14691798</v>
       </c>
       <c r="G253" s="25"/>
@@ -10452,7 +10479,7 @@
       <c r="E254" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F254" s="24">
+      <c r="F254" s="50">
         <v>16461125</v>
       </c>
       <c r="G254" s="25"/>
@@ -10476,7 +10503,7 @@
       <c r="E255" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F255" s="24">
+      <c r="F255" s="50">
         <v>17483605</v>
       </c>
       <c r="G255" s="25"/>
@@ -10500,7 +10527,7 @@
       <c r="E256" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F256" s="24">
+      <c r="F256" s="50">
         <v>18299769</v>
       </c>
       <c r="G256" s="25"/>
@@ -10524,7 +10551,7 @@
       <c r="E257" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F257" s="24">
+      <c r="F257" s="50">
         <v>19078116</v>
       </c>
       <c r="G257" s="25"/>
@@ -10548,7 +10575,7 @@
       <c r="E258" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F258" s="24">
+      <c r="F258" s="50">
         <v>24987945</v>
       </c>
       <c r="G258" s="25"/>
@@ -10572,7 +10599,7 @@
       <c r="E259" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F259" s="24">
+      <c r="F259" s="50">
         <v>29109060</v>
       </c>
       <c r="G259" s="25"/>
@@ -10596,7 +10623,7 @@
       <c r="E260" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F260" s="24">
+      <c r="F260" s="50">
         <v>32664248</v>
       </c>
       <c r="G260" s="25"/>
@@ -10620,7 +10647,7 @@
       <c r="E261" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F261" s="24">
+      <c r="F261" s="50">
         <v>49234940</v>
       </c>
       <c r="G261" s="25"/>
@@ -10644,7 +10671,7 @@
       <c r="E262" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F262" s="24">
+      <c r="F262" s="50">
         <v>51137926</v>
       </c>
       <c r="G262" s="25"/>
@@ -10668,7 +10695,7 @@
       <c r="E263" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F263" s="24">
+      <c r="F263" s="50">
         <v>55644729</v>
       </c>
       <c r="G263" s="25"/>
@@ -10692,7 +10719,7 @@
       <c r="E264" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F264" s="24">
+      <c r="F264" s="50">
         <v>90205369</v>
       </c>
       <c r="G264" s="25"/>
@@ -10716,7 +10743,7 @@
       <c r="E265" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F265" s="24">
+      <c r="F265" s="50">
         <v>93781294</v>
       </c>
       <c r="G265" s="25"/>
@@ -10740,7 +10767,7 @@
       <c r="E266" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F266" s="24">
+      <c r="F266" s="50">
         <v>106800000</v>
       </c>
       <c r="G266" s="25"/>
@@ -10764,7 +10791,7 @@
       <c r="E267" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F267" s="24">
+      <c r="F267" s="50">
         <v>120372075</v>
       </c>
       <c r="G267" s="25"/>
@@ -10788,7 +10815,7 @@
       <c r="E268" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F268" s="24">
+      <c r="F268" s="50">
         <v>301812800</v>
       </c>
       <c r="G268" s="25"/>
@@ -10812,7 +10839,7 @@
       <c r="E269" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F269" s="24">
+      <c r="F269" s="50">
         <v>902489702</v>
       </c>
       <c r="G269" s="25"/>
@@ -10836,7 +10863,7 @@
       <c r="E270" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="F270" s="24">
+      <c r="F270" s="50">
         <v>1010358200</v>
       </c>
       <c r="G270" s="25"/>
@@ -10861,7 +10888,7 @@
         <v>293</v>
       </c>
       <c r="F271" s="25"/>
-      <c r="G271" s="24">
+      <c r="G271" s="51">
         <v>276600000</v>
       </c>
       <c r="H271" s="13" t="s">
@@ -10885,7 +10912,7 @@
         <v>386</v>
       </c>
       <c r="F272" s="25"/>
-      <c r="G272" s="24">
+      <c r="G272" s="51">
         <v>1</v>
       </c>
       <c r="H272" s="13" t="s">
@@ -10909,7 +10936,7 @@
         <v>291</v>
       </c>
       <c r="F273" s="25"/>
-      <c r="G273" s="24">
+      <c r="G273" s="51">
         <v>799200000</v>
       </c>
       <c r="H273" s="13" t="s">
@@ -10933,7 +10960,7 @@
         <v>354</v>
       </c>
       <c r="F274" s="25"/>
-      <c r="G274" s="24">
+      <c r="G274" s="51">
         <v>65</v>
       </c>
       <c r="H274" s="13" t="s">
@@ -10957,7 +10984,7 @@
         <v>356</v>
       </c>
       <c r="F275" s="25"/>
-      <c r="G275" s="24">
+      <c r="G275" s="51">
         <v>33</v>
       </c>
       <c r="H275" s="13" t="s">
@@ -10981,7 +11008,7 @@
         <v>392</v>
       </c>
       <c r="F276" s="25"/>
-      <c r="G276" s="24">
+      <c r="G276" s="51">
         <v>202</v>
       </c>
       <c r="H276" s="13" t="s">
@@ -11005,7 +11032,7 @@
         <v>358</v>
       </c>
       <c r="F277" s="25"/>
-      <c r="G277" s="24">
+      <c r="G277" s="51">
         <v>438</v>
       </c>
       <c r="H277" s="13" t="s">
@@ -11029,7 +11056,7 @@
         <v>360</v>
       </c>
       <c r="F278" s="25"/>
-      <c r="G278" s="24">
+      <c r="G278" s="51">
         <v>53</v>
       </c>
       <c r="H278" s="13" t="s">
@@ -11053,7 +11080,7 @@
         <v>362</v>
       </c>
       <c r="F279" s="25"/>
-      <c r="G279" s="24">
+      <c r="G279" s="51">
         <v>25</v>
       </c>
       <c r="H279" s="13" t="s">
@@ -11077,7 +11104,7 @@
         <v>297</v>
       </c>
       <c r="F280" s="25"/>
-      <c r="G280" s="24">
+      <c r="G280" s="51">
         <v>34624096</v>
       </c>
       <c r="H280" s="13" t="s">
@@ -11101,7 +11128,7 @@
         <v>390</v>
       </c>
       <c r="F281" s="25"/>
-      <c r="G281" s="24">
+      <c r="G281" s="51">
         <v>199382000</v>
       </c>
       <c r="H281" s="13" t="s">
@@ -11125,7 +11152,7 @@
         <v>375</v>
       </c>
       <c r="F282" s="25"/>
-      <c r="G282" s="24">
+      <c r="G282" s="51">
         <v>46181</v>
       </c>
       <c r="H282" s="13" t="s">
@@ -11149,7 +11176,7 @@
         <v>397</v>
       </c>
       <c r="F283" s="25"/>
-      <c r="G283" s="24">
+      <c r="G283" s="51">
         <v>1633642</v>
       </c>
       <c r="H283" s="13" t="s">
@@ -11173,7 +11200,7 @@
         <v>382</v>
       </c>
       <c r="F284" s="25"/>
-      <c r="G284" s="24">
+      <c r="G284" s="51">
         <v>12</v>
       </c>
       <c r="H284" s="13" t="s">
@@ -11197,7 +11224,7 @@
         <v>311</v>
       </c>
       <c r="F285" s="25"/>
-      <c r="G285" s="24">
+      <c r="G285" s="51">
         <v>276600000</v>
       </c>
       <c r="H285" s="13" t="s">
@@ -11221,7 +11248,7 @@
         <v>309</v>
       </c>
       <c r="F286" s="25"/>
-      <c r="G286" s="24">
+      <c r="G286" s="51">
         <v>799200000</v>
       </c>
       <c r="H286" s="13" t="s">
@@ -11245,7 +11272,7 @@
         <v>313</v>
       </c>
       <c r="F287" s="25"/>
-      <c r="G287" s="24">
+      <c r="G287" s="51">
         <v>9030318</v>
       </c>
       <c r="H287" s="13" t="s">
@@ -11269,7 +11296,7 @@
         <v>315</v>
       </c>
       <c r="F288" s="25"/>
-      <c r="G288" s="24">
+      <c r="G288" s="51">
         <v>52</v>
       </c>
       <c r="H288" s="13" t="s">
@@ -11293,7 +11320,7 @@
         <v>384</v>
       </c>
       <c r="F289" s="25"/>
-      <c r="G289" s="24">
+      <c r="G289" s="51">
         <v>1</v>
       </c>
       <c r="H289" s="13" t="s">
@@ -11317,7 +11344,7 @@
         <v>295</v>
       </c>
       <c r="F290" s="25"/>
-      <c r="G290" s="24">
+      <c r="G290" s="51">
         <v>103</v>
       </c>
       <c r="H290" s="13" t="s">
@@ -11341,7 +11368,7 @@
         <v>304</v>
       </c>
       <c r="F291" s="25"/>
-      <c r="G291" s="24">
+      <c r="G291" s="51">
         <v>169</v>
       </c>
       <c r="H291" s="13" t="s">
@@ -11365,7 +11392,7 @@
         <v>302</v>
       </c>
       <c r="F292" s="25"/>
-      <c r="G292" s="24">
+      <c r="G292" s="51">
         <v>84</v>
       </c>
       <c r="H292" s="13" t="s">
@@ -11389,7 +11416,7 @@
         <v>373</v>
       </c>
       <c r="F293" s="25"/>
-      <c r="G293" s="24">
+      <c r="G293" s="51">
         <v>25</v>
       </c>
       <c r="H293" s="13" t="s">
@@ -11413,14 +11440,14 @@
         <v>388</v>
       </c>
       <c r="F294" s="25"/>
-      <c r="G294" s="24">
+      <c r="G294" s="51">
         <v>729000000</v>
       </c>
       <c r="H294" s="13" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="295" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="10" t="s">
         <v>139</v>
       </c>
@@ -11437,7 +11464,7 @@
         <v>395</v>
       </c>
       <c r="F295" s="25"/>
-      <c r="G295" s="24">
+      <c r="G295" s="52">
         <v>86064000</v>
       </c>
       <c r="H295" s="13" t="s">
@@ -12167,13 +12194,13 @@
       </c>
     </row>
     <row r="330" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A330" s="31" t="s">
+      <c r="A330" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="B330" s="32"/>
-      <c r="C330" s="32"/>
-      <c r="D330" s="32"/>
-      <c r="E330" s="33"/>
+      <c r="B330" s="34"/>
+      <c r="C330" s="34"/>
+      <c r="D330" s="34"/>
+      <c r="E330" s="35"/>
       <c r="F330" s="23">
         <v>386865713</v>
       </c>
@@ -12183,13 +12210,13 @@
       <c r="H330" s="8"/>
     </row>
     <row r="331" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A331" s="31" t="s">
+      <c r="A331" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="B331" s="32"/>
-      <c r="C331" s="32"/>
-      <c r="D331" s="32"/>
-      <c r="E331" s="33"/>
+      <c r="B331" s="34"/>
+      <c r="C331" s="34"/>
+      <c r="D331" s="34"/>
+      <c r="E331" s="35"/>
       <c r="F331" s="22"/>
       <c r="G331" s="23">
         <v>6399790387</v>
@@ -12197,25 +12224,25 @@
       <c r="H331" s="8"/>
     </row>
     <row r="332" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A332" s="43" t="s">
+      <c r="A332" s="38" t="s">
         <v>421</v>
       </c>
-      <c r="B332" s="44"/>
-      <c r="C332" s="44"/>
-      <c r="D332" s="44"/>
-      <c r="E332" s="44"/>
-      <c r="F332" s="44"/>
-      <c r="G332" s="44"/>
-      <c r="H332" s="45"/>
+      <c r="B332" s="39"/>
+      <c r="C332" s="39"/>
+      <c r="D332" s="39"/>
+      <c r="E332" s="39"/>
+      <c r="F332" s="39"/>
+      <c r="G332" s="39"/>
+      <c r="H332" s="40"/>
     </row>
     <row r="333" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A333" s="31" t="s">
+      <c r="A333" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B333" s="32"/>
-      <c r="C333" s="32"/>
-      <c r="D333" s="32"/>
-      <c r="E333" s="33"/>
+      <c r="B333" s="34"/>
+      <c r="C333" s="34"/>
+      <c r="D333" s="34"/>
+      <c r="E333" s="35"/>
       <c r="F333" s="22"/>
       <c r="G333" s="23">
         <v>224471112</v>
@@ -12247,13 +12274,13 @@
       </c>
     </row>
     <row r="335" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A335" s="31" t="s">
+      <c r="A335" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="B335" s="32"/>
-      <c r="C335" s="32"/>
-      <c r="D335" s="32"/>
-      <c r="E335" s="33"/>
+      <c r="B335" s="34"/>
+      <c r="C335" s="34"/>
+      <c r="D335" s="34"/>
+      <c r="E335" s="35"/>
       <c r="F335" s="22"/>
       <c r="G335" s="23">
         <v>5650687</v>
@@ -12261,13 +12288,13 @@
       <c r="H335" s="8"/>
     </row>
     <row r="336" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A336" s="31" t="s">
+      <c r="A336" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="B336" s="32"/>
-      <c r="C336" s="32"/>
-      <c r="D336" s="32"/>
-      <c r="E336" s="33"/>
+      <c r="B336" s="34"/>
+      <c r="C336" s="34"/>
+      <c r="D336" s="34"/>
+      <c r="E336" s="35"/>
       <c r="F336" s="22"/>
       <c r="G336" s="23">
         <v>230121799</v>
@@ -12275,25 +12302,25 @@
       <c r="H336" s="8"/>
     </row>
     <row r="337" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A337" s="43" t="s">
+      <c r="A337" s="38" t="s">
         <v>423</v>
       </c>
-      <c r="B337" s="44"/>
-      <c r="C337" s="44"/>
-      <c r="D337" s="44"/>
-      <c r="E337" s="44"/>
-      <c r="F337" s="44"/>
-      <c r="G337" s="44"/>
-      <c r="H337" s="45"/>
+      <c r="B337" s="39"/>
+      <c r="C337" s="39"/>
+      <c r="D337" s="39"/>
+      <c r="E337" s="39"/>
+      <c r="F337" s="39"/>
+      <c r="G337" s="39"/>
+      <c r="H337" s="40"/>
     </row>
     <row r="338" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A338" s="31" t="s">
+      <c r="A338" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B338" s="32"/>
-      <c r="C338" s="32"/>
-      <c r="D338" s="32"/>
-      <c r="E338" s="33"/>
+      <c r="B338" s="34"/>
+      <c r="C338" s="34"/>
+      <c r="D338" s="34"/>
+      <c r="E338" s="35"/>
       <c r="F338" s="22"/>
       <c r="G338" s="23">
         <v>333381749</v>
@@ -12325,13 +12352,13 @@
       </c>
     </row>
     <row r="340" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A340" s="31" t="s">
+      <c r="A340" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="B340" s="32"/>
-      <c r="C340" s="32"/>
-      <c r="D340" s="32"/>
-      <c r="E340" s="33"/>
+      <c r="B340" s="34"/>
+      <c r="C340" s="34"/>
+      <c r="D340" s="34"/>
+      <c r="E340" s="35"/>
       <c r="F340" s="22"/>
       <c r="G340" s="23">
         <v>12789477</v>
@@ -12339,13 +12366,13 @@
       <c r="H340" s="8"/>
     </row>
     <row r="341" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A341" s="31" t="s">
+      <c r="A341" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="B341" s="32"/>
-      <c r="C341" s="32"/>
-      <c r="D341" s="32"/>
-      <c r="E341" s="33"/>
+      <c r="B341" s="34"/>
+      <c r="C341" s="34"/>
+      <c r="D341" s="34"/>
+      <c r="E341" s="35"/>
       <c r="F341" s="22"/>
       <c r="G341" s="23">
         <v>346171226</v>
@@ -12353,25 +12380,25 @@
       <c r="H341" s="8"/>
     </row>
     <row r="342" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A342" s="43" t="s">
+      <c r="A342" s="38" t="s">
         <v>425</v>
       </c>
-      <c r="B342" s="44"/>
-      <c r="C342" s="44"/>
-      <c r="D342" s="44"/>
-      <c r="E342" s="44"/>
-      <c r="F342" s="44"/>
-      <c r="G342" s="44"/>
-      <c r="H342" s="45"/>
+      <c r="B342" s="39"/>
+      <c r="C342" s="39"/>
+      <c r="D342" s="39"/>
+      <c r="E342" s="39"/>
+      <c r="F342" s="39"/>
+      <c r="G342" s="39"/>
+      <c r="H342" s="40"/>
     </row>
     <row r="343" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A343" s="31" t="s">
+      <c r="A343" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B343" s="32"/>
-      <c r="C343" s="32"/>
-      <c r="D343" s="32"/>
-      <c r="E343" s="33"/>
+      <c r="B343" s="34"/>
+      <c r="C343" s="34"/>
+      <c r="D343" s="34"/>
+      <c r="E343" s="35"/>
       <c r="F343" s="22"/>
       <c r="G343" s="23">
         <v>94235006</v>
@@ -12403,13 +12430,13 @@
       </c>
     </row>
     <row r="345" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A345" s="31" t="s">
+      <c r="A345" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="B345" s="32"/>
-      <c r="C345" s="32"/>
-      <c r="D345" s="32"/>
-      <c r="E345" s="33"/>
+      <c r="B345" s="34"/>
+      <c r="C345" s="34"/>
+      <c r="D345" s="34"/>
+      <c r="E345" s="35"/>
       <c r="F345" s="22"/>
       <c r="G345" s="23">
         <v>6574975</v>
@@ -12417,13 +12444,13 @@
       <c r="H345" s="8"/>
     </row>
     <row r="346" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A346" s="31" t="s">
+      <c r="A346" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="B346" s="32"/>
-      <c r="C346" s="32"/>
-      <c r="D346" s="32"/>
-      <c r="E346" s="33"/>
+      <c r="B346" s="34"/>
+      <c r="C346" s="34"/>
+      <c r="D346" s="34"/>
+      <c r="E346" s="35"/>
       <c r="F346" s="22"/>
       <c r="G346" s="23">
         <v>100809981</v>
@@ -12431,25 +12458,25 @@
       <c r="H346" s="8"/>
     </row>
     <row r="347" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A347" s="43" t="s">
+      <c r="A347" s="38" t="s">
         <v>427</v>
       </c>
-      <c r="B347" s="44"/>
-      <c r="C347" s="44"/>
-      <c r="D347" s="44"/>
-      <c r="E347" s="44"/>
-      <c r="F347" s="44"/>
-      <c r="G347" s="44"/>
-      <c r="H347" s="45"/>
+      <c r="B347" s="39"/>
+      <c r="C347" s="39"/>
+      <c r="D347" s="39"/>
+      <c r="E347" s="39"/>
+      <c r="F347" s="39"/>
+      <c r="G347" s="39"/>
+      <c r="H347" s="40"/>
     </row>
     <row r="348" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A348" s="31" t="s">
+      <c r="A348" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B348" s="32"/>
-      <c r="C348" s="32"/>
-      <c r="D348" s="32"/>
-      <c r="E348" s="33"/>
+      <c r="B348" s="34"/>
+      <c r="C348" s="34"/>
+      <c r="D348" s="34"/>
+      <c r="E348" s="35"/>
       <c r="F348" s="23">
         <v>2833026200</v>
       </c>
@@ -12505,13 +12532,13 @@
       </c>
     </row>
     <row r="351" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A351" s="31" t="s">
+      <c r="A351" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="B351" s="32"/>
-      <c r="C351" s="32"/>
-      <c r="D351" s="32"/>
-      <c r="E351" s="33"/>
+      <c r="B351" s="34"/>
+      <c r="C351" s="34"/>
+      <c r="D351" s="34"/>
+      <c r="E351" s="35"/>
       <c r="F351" s="23">
         <v>2514378</v>
       </c>
@@ -12521,13 +12548,13 @@
       <c r="H351" s="8"/>
     </row>
     <row r="352" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A352" s="31" t="s">
+      <c r="A352" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="B352" s="32"/>
-      <c r="C352" s="32"/>
-      <c r="D352" s="32"/>
-      <c r="E352" s="33"/>
+      <c r="B352" s="34"/>
+      <c r="C352" s="34"/>
+      <c r="D352" s="34"/>
+      <c r="E352" s="35"/>
       <c r="F352" s="23">
         <v>2835508929</v>
       </c>
@@ -12535,25 +12562,25 @@
       <c r="H352" s="8"/>
     </row>
     <row r="353" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A353" s="43" t="s">
+      <c r="A353" s="38" t="s">
         <v>430</v>
       </c>
-      <c r="B353" s="44"/>
-      <c r="C353" s="44"/>
-      <c r="D353" s="44"/>
-      <c r="E353" s="44"/>
-      <c r="F353" s="44"/>
-      <c r="G353" s="44"/>
-      <c r="H353" s="45"/>
+      <c r="B353" s="39"/>
+      <c r="C353" s="39"/>
+      <c r="D353" s="39"/>
+      <c r="E353" s="39"/>
+      <c r="F353" s="39"/>
+      <c r="G353" s="39"/>
+      <c r="H353" s="40"/>
     </row>
     <row r="354" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A354" s="31" t="s">
+      <c r="A354" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B354" s="32"/>
-      <c r="C354" s="32"/>
-      <c r="D354" s="32"/>
-      <c r="E354" s="33"/>
+      <c r="B354" s="34"/>
+      <c r="C354" s="34"/>
+      <c r="D354" s="34"/>
+      <c r="E354" s="35"/>
       <c r="F354" s="22"/>
       <c r="G354" s="23">
         <v>35669605405</v>
@@ -12561,25 +12588,25 @@
       <c r="H354" s="8"/>
     </row>
     <row r="355" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A355" s="31" t="s">
+      <c r="A355" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="B355" s="32"/>
-      <c r="C355" s="32"/>
-      <c r="D355" s="32"/>
-      <c r="E355" s="33"/>
+      <c r="B355" s="34"/>
+      <c r="C355" s="34"/>
+      <c r="D355" s="34"/>
+      <c r="E355" s="35"/>
       <c r="F355" s="22"/>
       <c r="G355" s="22"/>
       <c r="H355" s="8"/>
     </row>
     <row r="356" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A356" s="31" t="s">
+      <c r="A356" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="B356" s="32"/>
-      <c r="C356" s="32"/>
-      <c r="D356" s="32"/>
-      <c r="E356" s="33"/>
+      <c r="B356" s="34"/>
+      <c r="C356" s="34"/>
+      <c r="D356" s="34"/>
+      <c r="E356" s="35"/>
       <c r="F356" s="22"/>
       <c r="G356" s="23">
         <v>35669605405</v>
@@ -12587,25 +12614,25 @@
       <c r="H356" s="8"/>
     </row>
     <row r="357" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A357" s="43" t="s">
+      <c r="A357" s="38" t="s">
         <v>431</v>
       </c>
-      <c r="B357" s="44"/>
-      <c r="C357" s="44"/>
-      <c r="D357" s="44"/>
-      <c r="E357" s="44"/>
-      <c r="F357" s="44"/>
-      <c r="G357" s="44"/>
-      <c r="H357" s="45"/>
+      <c r="B357" s="39"/>
+      <c r="C357" s="39"/>
+      <c r="D357" s="39"/>
+      <c r="E357" s="39"/>
+      <c r="F357" s="39"/>
+      <c r="G357" s="39"/>
+      <c r="H357" s="40"/>
     </row>
     <row r="358" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A358" s="31" t="s">
+      <c r="A358" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B358" s="32"/>
-      <c r="C358" s="32"/>
-      <c r="D358" s="32"/>
-      <c r="E358" s="33"/>
+      <c r="B358" s="34"/>
+      <c r="C358" s="34"/>
+      <c r="D358" s="34"/>
+      <c r="E358" s="35"/>
       <c r="F358" s="23">
         <v>2522257803</v>
       </c>
@@ -12613,25 +12640,25 @@
       <c r="H358" s="8"/>
     </row>
     <row r="359" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A359" s="31" t="s">
+      <c r="A359" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="B359" s="32"/>
-      <c r="C359" s="32"/>
-      <c r="D359" s="32"/>
-      <c r="E359" s="33"/>
+      <c r="B359" s="34"/>
+      <c r="C359" s="34"/>
+      <c r="D359" s="34"/>
+      <c r="E359" s="35"/>
       <c r="F359" s="22"/>
       <c r="G359" s="22"/>
       <c r="H359" s="8"/>
     </row>
     <row r="360" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A360" s="31" t="s">
+      <c r="A360" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="B360" s="32"/>
-      <c r="C360" s="32"/>
-      <c r="D360" s="32"/>
-      <c r="E360" s="33"/>
+      <c r="B360" s="34"/>
+      <c r="C360" s="34"/>
+      <c r="D360" s="34"/>
+      <c r="E360" s="35"/>
       <c r="F360" s="23">
         <v>2522257803</v>
       </c>
@@ -12639,25 +12666,25 @@
       <c r="H360" s="8"/>
     </row>
     <row r="361" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A361" s="43" t="s">
+      <c r="A361" s="38" t="s">
         <v>432</v>
       </c>
-      <c r="B361" s="44"/>
-      <c r="C361" s="44"/>
-      <c r="D361" s="44"/>
-      <c r="E361" s="44"/>
-      <c r="F361" s="44"/>
-      <c r="G361" s="44"/>
-      <c r="H361" s="45"/>
+      <c r="B361" s="39"/>
+      <c r="C361" s="39"/>
+      <c r="D361" s="39"/>
+      <c r="E361" s="39"/>
+      <c r="F361" s="39"/>
+      <c r="G361" s="39"/>
+      <c r="H361" s="40"/>
     </row>
     <row r="362" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A362" s="31" t="s">
+      <c r="A362" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B362" s="32"/>
-      <c r="C362" s="32"/>
-      <c r="D362" s="32"/>
-      <c r="E362" s="33"/>
+      <c r="B362" s="34"/>
+      <c r="C362" s="34"/>
+      <c r="D362" s="34"/>
+      <c r="E362" s="35"/>
       <c r="F362" s="22"/>
       <c r="G362" s="23">
         <v>14445007472</v>
@@ -13793,13 +13820,13 @@
       </c>
     </row>
     <row r="410" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A410" s="31" t="s">
+      <c r="A410" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="B410" s="32"/>
-      <c r="C410" s="32"/>
-      <c r="D410" s="32"/>
-      <c r="E410" s="33"/>
+      <c r="B410" s="34"/>
+      <c r="C410" s="34"/>
+      <c r="D410" s="34"/>
+      <c r="E410" s="35"/>
       <c r="F410" s="23">
         <v>6490020032</v>
       </c>
@@ -13809,13 +13836,13 @@
       <c r="H410" s="8"/>
     </row>
     <row r="411" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A411" s="31" t="s">
+      <c r="A411" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="B411" s="32"/>
-      <c r="C411" s="32"/>
-      <c r="D411" s="32"/>
-      <c r="E411" s="33"/>
+      <c r="B411" s="34"/>
+      <c r="C411" s="34"/>
+      <c r="D411" s="34"/>
+      <c r="E411" s="35"/>
       <c r="F411" s="22"/>
       <c r="G411" s="23">
         <v>8767045071</v>
@@ -13823,25 +13850,25 @@
       <c r="H411" s="8"/>
     </row>
     <row r="412" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A412" s="43" t="s">
+      <c r="A412" s="38" t="s">
         <v>489</v>
       </c>
-      <c r="B412" s="44"/>
-      <c r="C412" s="44"/>
-      <c r="D412" s="44"/>
-      <c r="E412" s="44"/>
-      <c r="F412" s="44"/>
-      <c r="G412" s="44"/>
-      <c r="H412" s="45"/>
+      <c r="B412" s="39"/>
+      <c r="C412" s="39"/>
+      <c r="D412" s="39"/>
+      <c r="E412" s="39"/>
+      <c r="F412" s="39"/>
+      <c r="G412" s="39"/>
+      <c r="H412" s="40"/>
     </row>
     <row r="413" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A413" s="31" t="s">
+      <c r="A413" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B413" s="32"/>
-      <c r="C413" s="32"/>
-      <c r="D413" s="32"/>
-      <c r="E413" s="33"/>
+      <c r="B413" s="34"/>
+      <c r="C413" s="34"/>
+      <c r="D413" s="34"/>
+      <c r="E413" s="35"/>
       <c r="F413" s="22"/>
       <c r="G413" s="22"/>
       <c r="H413" s="8"/>
@@ -13895,13 +13922,13 @@
       </c>
     </row>
     <row r="416" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A416" s="31" t="s">
+      <c r="A416" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="B416" s="32"/>
-      <c r="C416" s="32"/>
-      <c r="D416" s="32"/>
-      <c r="E416" s="33"/>
+      <c r="B416" s="34"/>
+      <c r="C416" s="34"/>
+      <c r="D416" s="34"/>
+      <c r="E416" s="35"/>
       <c r="F416" s="23">
         <v>9821257247</v>
       </c>
@@ -13909,13 +13936,13 @@
       <c r="H416" s="8"/>
     </row>
     <row r="417" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A417" s="31" t="s">
+      <c r="A417" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="B417" s="32"/>
-      <c r="C417" s="32"/>
-      <c r="D417" s="32"/>
-      <c r="E417" s="33"/>
+      <c r="B417" s="34"/>
+      <c r="C417" s="34"/>
+      <c r="D417" s="34"/>
+      <c r="E417" s="35"/>
       <c r="F417" s="23">
         <v>9821257247</v>
       </c>
@@ -13923,25 +13950,25 @@
       <c r="H417" s="8"/>
     </row>
     <row r="418" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A418" s="43" t="s">
+      <c r="A418" s="38" t="s">
         <v>494</v>
       </c>
-      <c r="B418" s="44"/>
-      <c r="C418" s="44"/>
-      <c r="D418" s="44"/>
-      <c r="E418" s="44"/>
-      <c r="F418" s="44"/>
-      <c r="G418" s="44"/>
-      <c r="H418" s="45"/>
+      <c r="B418" s="39"/>
+      <c r="C418" s="39"/>
+      <c r="D418" s="39"/>
+      <c r="E418" s="39"/>
+      <c r="F418" s="39"/>
+      <c r="G418" s="39"/>
+      <c r="H418" s="40"/>
     </row>
     <row r="419" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A419" s="31" t="s">
+      <c r="A419" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B419" s="32"/>
-      <c r="C419" s="32"/>
-      <c r="D419" s="32"/>
-      <c r="E419" s="33"/>
+      <c r="B419" s="34"/>
+      <c r="C419" s="34"/>
+      <c r="D419" s="34"/>
+      <c r="E419" s="35"/>
       <c r="F419" s="22"/>
       <c r="G419" s="23">
         <v>764421481235</v>
@@ -13949,25 +13976,25 @@
       <c r="H419" s="8"/>
     </row>
     <row r="420" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A420" s="31" t="s">
+      <c r="A420" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="B420" s="32"/>
-      <c r="C420" s="32"/>
-      <c r="D420" s="32"/>
-      <c r="E420" s="33"/>
+      <c r="B420" s="34"/>
+      <c r="C420" s="34"/>
+      <c r="D420" s="34"/>
+      <c r="E420" s="35"/>
       <c r="F420" s="22"/>
       <c r="G420" s="22"/>
       <c r="H420" s="8"/>
     </row>
     <row r="421" spans="1:8" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A421" s="31" t="s">
+      <c r="A421" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="B421" s="32"/>
-      <c r="C421" s="32"/>
-      <c r="D421" s="32"/>
-      <c r="E421" s="33"/>
+      <c r="B421" s="34"/>
+      <c r="C421" s="34"/>
+      <c r="D421" s="34"/>
+      <c r="E421" s="35"/>
       <c r="F421" s="22"/>
       <c r="G421" s="23">
         <v>764421481235</v>
@@ -14007,16 +14034,16 @@
       <c r="D424" s="8"/>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A425" s="46" t="s">
+      <c r="A425" s="36" t="s">
         <v>502</v>
       </c>
-      <c r="B425" s="47"/>
-      <c r="C425" s="47"/>
-      <c r="D425" s="47"/>
-      <c r="E425" s="47"/>
-      <c r="F425" s="47"/>
-      <c r="G425" s="47"/>
-      <c r="H425" s="47"/>
+      <c r="B425" s="37"/>
+      <c r="C425" s="37"/>
+      <c r="D425" s="37"/>
+      <c r="E425" s="37"/>
+      <c r="F425" s="37"/>
+      <c r="G425" s="37"/>
+      <c r="H425" s="37"/>
     </row>
     <row r="426" spans="1:8" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" s="1"/>
@@ -14089,15 +14116,45 @@
     <sortCondition ref="E271:E295"/>
   </sortState>
   <mergeCells count="60">
-    <mergeCell ref="A420:E420"/>
-    <mergeCell ref="A421:E421"/>
-    <mergeCell ref="A425:H425"/>
-    <mergeCell ref="A412:H412"/>
-    <mergeCell ref="A413:E413"/>
-    <mergeCell ref="A416:E416"/>
-    <mergeCell ref="A417:E417"/>
-    <mergeCell ref="A418:H418"/>
-    <mergeCell ref="A419:E419"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A85:H85"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A115:H115"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A124:E124"/>
+    <mergeCell ref="A125:E125"/>
+    <mergeCell ref="A126:H126"/>
+    <mergeCell ref="A336:E336"/>
+    <mergeCell ref="A330:E330"/>
+    <mergeCell ref="A331:E331"/>
+    <mergeCell ref="A332:H332"/>
+    <mergeCell ref="A333:E333"/>
+    <mergeCell ref="A335:E335"/>
+    <mergeCell ref="A352:E352"/>
+    <mergeCell ref="A337:H337"/>
+    <mergeCell ref="A338:E338"/>
+    <mergeCell ref="A340:E340"/>
+    <mergeCell ref="A341:E341"/>
+    <mergeCell ref="A342:H342"/>
+    <mergeCell ref="A343:E343"/>
+    <mergeCell ref="A345:E345"/>
+    <mergeCell ref="A346:E346"/>
+    <mergeCell ref="A347:H347"/>
+    <mergeCell ref="A348:E348"/>
+    <mergeCell ref="A351:E351"/>
     <mergeCell ref="A411:E411"/>
     <mergeCell ref="A353:H353"/>
     <mergeCell ref="A354:E354"/>
@@ -14110,45 +14167,15 @@
     <mergeCell ref="A361:H361"/>
     <mergeCell ref="A362:E362"/>
     <mergeCell ref="A410:E410"/>
-    <mergeCell ref="A352:E352"/>
-    <mergeCell ref="A337:H337"/>
-    <mergeCell ref="A338:E338"/>
-    <mergeCell ref="A340:E340"/>
-    <mergeCell ref="A341:E341"/>
-    <mergeCell ref="A342:H342"/>
-    <mergeCell ref="A343:E343"/>
-    <mergeCell ref="A345:E345"/>
-    <mergeCell ref="A346:E346"/>
-    <mergeCell ref="A347:H347"/>
-    <mergeCell ref="A348:E348"/>
-    <mergeCell ref="A351:E351"/>
-    <mergeCell ref="A116:E116"/>
-    <mergeCell ref="A124:E124"/>
-    <mergeCell ref="A125:E125"/>
-    <mergeCell ref="A126:H126"/>
-    <mergeCell ref="A336:E336"/>
-    <mergeCell ref="A330:E330"/>
-    <mergeCell ref="A331:E331"/>
-    <mergeCell ref="A332:H332"/>
-    <mergeCell ref="A333:E333"/>
-    <mergeCell ref="A335:E335"/>
-    <mergeCell ref="A85:H85"/>
-    <mergeCell ref="A86:E86"/>
-    <mergeCell ref="A113:E113"/>
-    <mergeCell ref="A114:E114"/>
-    <mergeCell ref="A115:H115"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A83:E83"/>
-    <mergeCell ref="A84:E84"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="A420:E420"/>
+    <mergeCell ref="A421:E421"/>
+    <mergeCell ref="A425:H425"/>
+    <mergeCell ref="A412:H412"/>
+    <mergeCell ref="A413:E413"/>
+    <mergeCell ref="A416:E416"/>
+    <mergeCell ref="A417:E417"/>
+    <mergeCell ref="A418:H418"/>
+    <mergeCell ref="A419:E419"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
